--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/mccv_confusion_matrix.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/mccv_confusion_matrix.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>66</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D2" t="n">
         <v>72</v>
       </c>
-      <c r="C2" t="n">
-        <v>2168</v>
-      </c>
-      <c r="D2" t="n">
-        <v>256</v>
-      </c>
       <c r="E2" t="n">
-        <v>576</v>
+        <v>946</v>
       </c>
     </row>
     <row r="3">
@@ -476,16 +476,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3" t="n">
-        <v>467</v>
+        <v>261</v>
       </c>
       <c r="D3" t="n">
-        <v>3224</v>
+        <v>2536</v>
       </c>
       <c r="E3" t="n">
-        <v>1309</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="4">
@@ -498,13 +498,13 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>830</v>
+        <v>941</v>
       </c>
       <c r="D4" t="n">
-        <v>2588</v>
+        <v>1608</v>
       </c>
       <c r="E4" t="n">
-        <v>582</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5">
@@ -517,13 +517,13 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>3465</v>
+        <v>3184</v>
       </c>
       <c r="D5" t="n">
-        <v>6068</v>
+        <v>4216</v>
       </c>
       <c r="E5" t="n">
-        <v>2467</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="6">

--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/mccv_confusion_matrix.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/mccv_confusion_matrix.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C2" t="n">
-        <v>1982</v>
+        <v>2108</v>
       </c>
       <c r="D2" t="n">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="E2" t="n">
-        <v>946</v>
+        <v>711</v>
       </c>
     </row>
     <row r="3">
@@ -476,16 +476,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C3" t="n">
-        <v>261</v>
+        <v>196</v>
       </c>
       <c r="D3" t="n">
-        <v>2536</v>
+        <v>2650</v>
       </c>
       <c r="E3" t="n">
-        <v>1203</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="4">
@@ -498,13 +498,13 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>941</v>
+        <v>892</v>
       </c>
       <c r="D4" t="n">
-        <v>1608</v>
+        <v>2503</v>
       </c>
       <c r="E4" t="n">
-        <v>451</v>
+        <v>605</v>
       </c>
     </row>
     <row r="5">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5" t="n">
-        <v>3184</v>
+        <v>3196</v>
       </c>
       <c r="D5" t="n">
-        <v>4216</v>
+        <v>5334</v>
       </c>
       <c r="E5" t="n">
-        <v>2600</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="6">

--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/mccv_confusion_matrix.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/mccv_confusion_matrix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,11 +444,6 @@
           <t>Cluster C2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster C3</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -457,16 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>2108</v>
+        <v>1503</v>
       </c>
       <c r="D2" t="n">
-        <v>181</v>
-      </c>
-      <c r="E2" t="n">
-        <v>711</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="3">
@@ -476,77 +468,50 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="C3" t="n">
-        <v>196</v>
+        <v>879</v>
       </c>
       <c r="D3" t="n">
-        <v>2650</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1154</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Cluster C3</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="C4" t="n">
-        <v>892</v>
+        <v>2382</v>
       </c>
       <c r="D4" t="n">
-        <v>2503</v>
-      </c>
-      <c r="E4" t="n">
-        <v>605</v>
+        <v>5618</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>49</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3196</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5334</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2470</v>
-      </c>
+      <c r="A5" s="1" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Combined results from 1,000 CV iterations (test size: 20%)</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Combined results from 1,000 CV iterations (test size: 20%)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
